--- a/reports/SOH_21_10_2026.xlsx
+++ b/reports/SOH_21_10_2026.xlsx
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>40000</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>40000</v>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>25000</v>
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>36000</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="D341" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E341" s="3" t="n">
         <v>3039</v>
@@ -10312,24 +10312,24 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>9333527464781</t>
+          <t>9333527583130</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>BL0668</t>
+          <t>AH4310</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>BUCKET COLLAPSIBLE 10L</t>
+          <t>BRUSH DETANGLING WITH MIRROR</t>
         </is>
       </c>
       <c r="D357" s="2" t="n">
-        <v>0</v>
+        <v>607</v>
       </c>
       <c r="E357" s="3" t="n">
-        <v>60509</v>
+        <v>9468</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -10368,24 +10368,24 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>9333527280473</t>
+          <t>9333527730305</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>SG0198</t>
+          <t>TG4153</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>BUBBLE WRAP CLEAR 30cmx3m</t>
+          <t>BUBBLE GATLING GUN 2ASSTD</t>
         </is>
       </c>
       <c r="D359" s="2" t="n">
-        <v>252</v>
+        <v>27</v>
       </c>
       <c r="E359" s="3" t="n">
-        <v>12205</v>
+        <v>31328</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -10396,24 +10396,24 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>9333527730305</t>
+          <t>9333527280473</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>TG4153</t>
+          <t>SG0198</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>BUBBLE GATLING GUN 2ASSTD</t>
+          <t>BUBBLE WRAP CLEAR 30cmx3m</t>
         </is>
       </c>
       <c r="D360" s="2" t="n">
-        <v>27</v>
+        <v>252</v>
       </c>
       <c r="E360" s="3" t="n">
-        <v>31328</v>
+        <v>12205</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -10424,24 +10424,24 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>9333527809018</t>
+          <t>9333527464781</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>TA0000002</t>
+          <t>BL0668</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>BUILDING CONNECTOR BLOCK 112PCS</t>
+          <t>BUCKET COLLAPSIBLE 10L</t>
         </is>
       </c>
       <c r="D361" s="2" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E361" s="3" t="n">
-        <v>17348</v>
+        <v>60509</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -10452,24 +10452,24 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>9333527583130</t>
+          <t>9333527809018</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>AH4310</t>
+          <t>TA0000002</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>BRUSH DETANGLING WITH MIRROR</t>
+          <t>BUILDING CONNECTOR BLOCK 112PCS</t>
         </is>
       </c>
       <c r="D362" s="2" t="n">
-        <v>607</v>
+        <v>43</v>
       </c>
       <c r="E362" s="3" t="n">
-        <v>9468</v>
+        <v>17348</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="D366" s="2" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E366" s="3" t="n">
         <v>16261</v>
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="D684" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E684" s="3" t="n">
         <v>13613</v>
@@ -21695,7 +21695,7 @@
         </is>
       </c>
       <c r="D763" s="2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E763" s="3" t="n">
         <v>22543</v>
@@ -40545,7 +40545,7 @@
         </is>
       </c>
       <c r="D1436" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E1436" s="3" t="n">
         <v>8156</v>
@@ -43569,7 +43569,7 @@
         </is>
       </c>
       <c r="D1544" s="2" t="n">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="E1544" s="3" t="n">
         <v>15250</v>
